--- a/research/MFB.NZ/Reports/MFB.NZ_DCF_Model.xlsx
+++ b/research/MFB.NZ/Reports/MFB.NZ_DCF_Model.xlsx
@@ -2436,9 +2436,10 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8">
-        <f> Reported (Owner) FCF per CSV</f>
-        <v>0</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>= Reported (Owner) FCF per CSV</t>
+        </is>
       </c>
       <c r="B8" s="5">
         <v>21.164</v>
@@ -2483,9 +2484,10 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="8">
-        <f> Owner FCF (SBC-adjusted)</f>
-        <v>0</v>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>= Owner FCF (SBC-adjusted)</t>
+        </is>
       </c>
       <c r="B10" s="5">
         <v>20.859</v>
